--- a/docs/import-examples/04 Cutlery and equipment.xlsx
+++ b/docs/import-examples/04 Cutlery and equipment.xlsx
@@ -47,6 +47,13 @@
     <comment ref="E1" authorId="0">
       <text>
         <r>
+          <t>Optional. What the client pays for one piece for one event, in rupees. Fills in on quotations.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
           <t>Optional. Where it is kept.</t>
         </r>
       </text>
@@ -56,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Item</t>
   </si>
@@ -68,6 +75,9 @@
   </si>
   <si>
     <t>Replacement cost</t>
+  </si>
+  <si>
+    <t>Rent per piece</t>
   </si>
   <si>
     <t>Storage location</t>
@@ -509,17 +519,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -535,13 +546,16 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>500</v>
@@ -549,16 +563,19 @@
       <c r="D2">
         <v>85</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -566,16 +583,19 @@
       <c r="D3">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
+      <c r="E3">
+        <v>1.5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -583,16 +603,19 @@
       <c r="D4">
         <v>2800</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
+      <c r="E4">
+        <v>150</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>60</v>
@@ -600,16 +623,19 @@
       <c r="D5">
         <v>350</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
+      <c r="E5">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -617,8 +643,11 @@
       <c r="D6">
         <v>9000</v>
       </c>
-      <c r="E6" t="s">
-        <v>18</v>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
